--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487741_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487741_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0429</v>
+        <v>6.0723</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2884</v>
+        <v>5.5086</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7544999999999999</v>
+        <v>0.5637</v>
       </c>
       <c r="G2" t="n">
         <v>4.6131</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7402</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>1.421</v>
+        <v>0.6412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3192</v>
+        <v>0.1285</v>
       </c>
       <c r="V2" t="n">
         <v>1.2716</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6479</v>
+        <v>6.0478</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8187</v>
+        <v>4.5184</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8291</v>
+        <v>1.5293</v>
       </c>
       <c r="G3" t="n">
         <v>5.1754</v>
@@ -688,13 +688,13 @@
         <v>0.5821</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8903</v>
+        <v>0.2902</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3163</v>
+        <v>0.016</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.2743</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0094</v>
+        <v>4.7702</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4615</v>
+        <v>3.5221</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5479</v>
+        <v>1.2481</v>
       </c>
       <c r="G4" t="n">
         <v>2.1068</v>
@@ -766,13 +766,13 @@
         <v>0.9702</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7086</v>
+        <v>0.4694</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1346</v>
+        <v>0.1951</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.2743</v>
       </c>
       <c r="V4" t="n">
         <v>1.2239</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5389</v>
+        <v>2.2813</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2911</v>
+        <v>1.2515</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2478</v>
+        <v>1.0298</v>
       </c>
       <c r="G5" t="n">
         <v>1.6204</v>
@@ -844,13 +844,13 @@
         <v>1.1642</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0065</v>
+        <v>0.7489</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0954</v>
+        <v>-0.1349</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1019</v>
+        <v>0.8838</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2821</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3855</v>
+        <v>1.7104</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6972</v>
+        <v>1.1854</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3117</v>
+        <v>0.525</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1153</v>
+        <v>3.817</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.365</v>
+        <v>0.9919</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2497</v>
+        <v>2.8251</v>
       </c>
       <c r="J6" t="n">
-        <v>0.093</v>
+        <v>3.2245</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0288</v>
+        <v>1.1946</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1218</v>
+        <v>2.0298</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2083</v>
+        <v>0.5925</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3362</v>
+        <v>-0.2027</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1279</v>
+        <v>0.7952</v>
       </c>
       <c r="P6" t="n">
-        <v>0.194</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1514</v>
+        <v>-0.1946</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1077</v>
+        <v>-0.3808</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0437</v>
+        <v>0.1862</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4582</v>
+        <v>-0.9418</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6821</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
         <v>-1.2239</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1771</v>
+        <v>1.5428</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9247</v>
+        <v>1.7182</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2525</v>
+        <v>-0.1754</v>
       </c>
       <c r="G7" t="n">
-        <v>3.817</v>
+        <v>-0.1153</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9919</v>
+        <v>-0.365</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8251</v>
+        <v>0.2497</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2245</v>
+        <v>0.093</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1946</v>
+        <v>-0.0288</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0298</v>
+        <v>0.1218</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5925</v>
+        <v>-0.2083</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2027</v>
+        <v>-0.3362</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7952</v>
+        <v>0.1279</v>
       </c>
       <c r="P7" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7279</v>
+        <v>0.0059</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.0867</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0863</v>
+        <v>0.0926</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9418</v>
+        <v>1.4582</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>2.6821</v>
       </c>
       <c r="X7" t="n">
         <v>-1.2239</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.206</v>
+        <v>0.8999</v>
       </c>
       <c r="E8" t="n">
-        <v>1.4081</v>
+        <v>1.8295</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2021</v>
+        <v>-0.9296</v>
       </c>
       <c r="G8" t="n">
         <v>1.0625</v>
@@ -1078,13 +1078,13 @@
         <v>1.3582</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3028</v>
+        <v>0.3911</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0134</v>
+        <v>0.4349</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3163</v>
+        <v>-0.0437</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9418</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>M. BATLLE BERNARDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.8114</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7914</v>
+        <v>-0.6554</v>
       </c>
       <c r="F9" t="n">
-        <v>1.8653</v>
+        <v>1.4668</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0975</v>
+        <v>0.8361</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4045</v>
+        <v>1.4055</v>
       </c>
       <c r="I9" t="n">
-        <v>0.307</v>
+        <v>-0.5694</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1068</v>
+        <v>0.1045</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1524</v>
+        <v>1.4747</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0456</v>
+        <v>-1.3702</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0092</v>
+        <v>0.7316</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2521</v>
+        <v>-0.0692</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2614</v>
+        <v>0.8008</v>
       </c>
       <c r="P9" t="n">
         <v>0.194</v>
@@ -1156,28 +1156,28 @@
         <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4002</v>
+        <v>-0.5008</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7145</v>
+        <v>-0.0718</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3143</v>
+        <v>-0.429</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3776</v>
+        <v>0.2821</v>
       </c>
       <c r="W9" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.3776</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BATLLE BERNARDO</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0446</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1769</v>
+        <v>-1.4305</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2215</v>
+        <v>2.0289</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8361</v>
+        <v>-0.0975</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4055</v>
+        <v>-0.4045</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5694</v>
+        <v>0.307</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1045</v>
+        <v>-0.1068</v>
       </c>
       <c r="K10" t="n">
-        <v>1.4747</v>
+        <v>-0.1524</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3702</v>
+        <v>0.0456</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7316</v>
+        <v>0.0092</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0692</v>
+        <v>-0.2521</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8008</v>
+        <v>0.2614</v>
       </c>
       <c r="P10" t="n">
         <v>0.194</v>
@@ -1234,22 +1234,22 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2676</v>
+        <v>0.1242</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5933</v>
+        <v>-0.3536</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6743</v>
+        <v>0.4778</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2821</v>
+        <v>0.3776</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1858</v>
+        <v>0.1144</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05</v>
+        <v>0.4319</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2358</v>
+        <v>-0.3175</v>
       </c>
       <c r="G11" t="n">
         <v>-0.0786</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3212</v>
+        <v>0.6214</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2042</v>
+        <v>0.1777</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5254</v>
+        <v>0.4436</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2343</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>23.9404</v>
+        <v>24.8488</v>
       </c>
       <c r="E12" t="n">
-        <v>16.9714</v>
+        <v>17.8797</v>
       </c>
       <c r="F12" t="n">
-        <v>6.968999999999999</v>
+        <v>6.9691</v>
       </c>
       <c r="G12" t="n">
         <v>18.9399</v>
@@ -1369,7 +1369,7 @@
         <v>11.7896</v>
       </c>
       <c r="L12" t="n">
-        <v>8.230699999999999</v>
+        <v>8.230700000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-1.0807</v>
@@ -1390,10 +1390,10 @@
         <v>11.642</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8169</v>
+        <v>2.7254</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4714000000000002</v>
+        <v>0.4370999999999999</v>
       </c>
       <c r="U12" t="n">
         <v>2.2884</v>
@@ -1402,7 +1402,7 @@
         <v>2.2134</v>
       </c>
       <c r="W12" t="n">
-        <v>8.094099999999999</v>
+        <v>8.094100000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-5.8807</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.0335</v>
+        <v>2.0063</v>
       </c>
       <c r="E13" t="n">
         <v>1.9843</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0493</v>
+        <v>0.022</v>
       </c>
       <c r="G13" t="n">
         <v>2.0035</v>
@@ -1468,13 +1468,13 @@
         <v>0.194</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.164</v>
+        <v>-0.1912</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U13" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.3251</v>
+        <v>0.2518</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6112</v>
+        <v>2.4101</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.2861</v>
+        <v>-2.1583</v>
       </c>
       <c r="G14" t="n">
         <v>-0.8023</v>
@@ -1546,13 +1546,13 @@
         <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6498</v>
+        <v>0.5765</v>
       </c>
       <c r="T14" t="n">
-        <v>1.5309</v>
+        <v>0.3297</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1189</v>
+        <v>0.2468</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6866</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-1.3254</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.239</v>
+        <v>-0.4392</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3956</v>
+        <v>-0.8862</v>
       </c>
       <c r="G15" t="n">
         <v>0.6827</v>
@@ -1624,13 +1624,13 @@
         <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0424</v>
+        <v>0.3516</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0617</v>
+        <v>-0.1385</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9807</v>
+        <v>0.4901</v>
       </c>
       <c r="V15" t="n">
         <v>-2.1657</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.705</v>
+        <v>-1.3625</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8468</v>
+        <v>-0.7467</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8582</v>
+        <v>-0.6157</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7347</v>
@@ -1702,13 +1702,13 @@
         <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7763</v>
+        <v>-0.4338</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5451</v>
+        <v>-0.445</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2313</v>
+        <v>0.0112</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0369</v>
+        <v>-1.6065</v>
       </c>
       <c r="E17" t="n">
         <v>0.06759999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1045</v>
+        <v>-1.6741</v>
       </c>
       <c r="G17" t="n">
         <v>-6.1421</v>
@@ -1780,13 +1780,13 @@
         <v>2.1344</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4843</v>
+        <v>-0.0538</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3489</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1354</v>
+        <v>0.295</v>
       </c>
       <c r="V17" t="n">
         <v>4.3955</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.8815</v>
+        <v>-1.9144</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7206</v>
+        <v>-0.3202</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1609</v>
+        <v>-1.5942</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7052</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3883</v>
+        <v>-0.4212</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7145</v>
+        <v>-0.3141</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6738</v>
+        <v>-0.1071</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5642</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>P. DOMINGUEZ LORENZO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.0372</v>
+        <v>-2.601</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5545</v>
+        <v>-2.6297</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4827</v>
+        <v>0.0287</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7143</v>
+        <v>-1.24</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.131</v>
+        <v>-0.3007</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.5833</v>
+        <v>-0.9393</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3908</v>
+        <v>0.8096</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0175</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6267</v>
+        <v>0.0228</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.105</v>
+        <v>-2.0496</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1485</v>
+        <v>-1.0875</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9565</v>
+        <v>-0.9621</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1642</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0363</v>
+        <v>-0.2849</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2288</v>
+        <v>-0.8109</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1925</v>
+        <v>0.526</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1224</v>
+        <v>0.2821</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. DOMINGUEZ LORENZO</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4563</v>
+        <v>-2.758</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0301</v>
+        <v>-0.3543</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4263</v>
+        <v>-2.4037</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.24</v>
+        <v>-1.7143</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3007</v>
+        <v>-0.131</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9393</v>
+        <v>-1.5833</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8096</v>
+        <v>0.3908</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7868000000000001</v>
+        <v>1.0175</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0228</v>
+        <v>-0.6267</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.0496</v>
+        <v>-2.105</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0875</v>
+        <v>-1.1485</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9621</v>
+        <v>-0.9565</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3582</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1402</v>
+        <v>0.2428</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2113</v>
+        <v>-0.0286</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0711</v>
+        <v>0.2714</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2821</v>
+        <v>-0.1224</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2821</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.3463</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.009</v>
+        <v>-4.9578</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2904</v>
+        <v>-2.5907</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7186</v>
+        <v>-2.3671</v>
       </c>
       <c r="G21" t="n">
         <v>-4.343</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2923</v>
+        <v>0.3435</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1839</v>
+        <v>-0.1164</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1084</v>
+        <v>0.4599</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3463</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.538500000000001</v>
+        <v>-7.671</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.9508</v>
+        <v>-4.3502</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.5877</v>
+        <v>-3.3208</v>
       </c>
       <c r="G22" t="n">
         <v>-4.9444</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8120000000000001</v>
+        <v>0.0555</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7739</v>
+        <v>-0.1733</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0381</v>
+        <v>0.2288</v>
       </c>
       <c r="V22" t="n">
         <v>-2.006</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-23.9404</v>
+        <v>-21.9385</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.9691</v>
+        <v>-6.969</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.9713</v>
+        <v>-14.9694</v>
       </c>
       <c r="G23" t="n">
         <v>-18.9398</v>
@@ -2248,13 +2248,13 @@
         <v>10.6717</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.8169</v>
+        <v>0.185</v>
       </c>
       <c r="T23" t="n">
         <v>-2.2883</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4713000000000003</v>
+        <v>2.4731</v>
       </c>
       <c r="V23" t="n">
         <v>-2.2136</v>
